--- a/Sensitivity_Output/Best_Per_Method.xlsx
+++ b/Sensitivity_Output/Best_Per_Method.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>avg_distance_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -507,22 +519,22 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>27.46</v>
+        <v>27.22</v>
       </c>
       <c r="G2" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J2" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -541,7 +553,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -553,22 +565,22 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>27.42</v>
+        <v>24.43</v>
       </c>
       <c r="G3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J3" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K3" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -602,19 +614,19 @@
         <v>20.23</v>
       </c>
       <c r="G4" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J4" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K4" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -648,19 +660,19 @@
         <v>27.14</v>
       </c>
       <c r="G5" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J5" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K5" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Best_Per_Method.xlsx
+++ b/Sensitivity_Output/Best_Per_Method.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>avg_distance_km</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>avg_travel_hours</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -507,22 +519,22 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>27.46</v>
+        <v>1.18</v>
       </c>
       <c r="G2" t="n">
-        <v>8.51</v>
+        <v>0.09</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>70.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J2" t="n">
-        <v>55.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>75.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -541,7 +553,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -553,22 +565,22 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>27.42</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>70.5</v>
+        <v>65.2</v>
       </c>
       <c r="J3" t="n">
-        <v>55.5</v>
+        <v>65.2</v>
       </c>
       <c r="K3" t="n">
-        <v>75.5</v>
+        <v>65.2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -599,22 +611,22 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="G4" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.5</v>
+        <v>63.4</v>
       </c>
       <c r="J4" t="n">
-        <v>52.4</v>
+        <v>64.8</v>
       </c>
       <c r="K4" t="n">
-        <v>78.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -645,22 +657,22 @@
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>71.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J5" t="n">
-        <v>52.6</v>
+        <v>65.2</v>
       </c>
       <c r="K5" t="n">
-        <v>77.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Best_Per_Method.xlsx
+++ b/Sensitivity_Output/Best_Per_Method.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
@@ -519,31 +519,31 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>65.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>65.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="K2" t="n">
-        <v>65.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
@@ -565,31 +565,31 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>65.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>65.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -611,31 +611,31 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G4" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>63.4</v>
+        <v>89.5</v>
       </c>
       <c r="J4" t="n">
-        <v>64.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>67.3</v>
+        <v>100.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -660,28 +660,28 @@
         <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>65.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>65.2</v>
+        <v>92.7</v>
       </c>
       <c r="K5" t="n">
-        <v>65.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity_Output/Best_Per_Method.xlsx
+++ b/Sensitivity_Output/Best_Per_Method.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
@@ -519,31 +519,31 @@
         <v>500</v>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>0.53</v>
       </c>
       <c r="G2" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>92.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>92.7</v>
+        <v>73.8</v>
       </c>
       <c r="K2" t="n">
-        <v>92.8</v>
+        <v>74</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -565,31 +565,31 @@
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G3" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>93.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J3" t="n">
-        <v>92.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K3" t="n">
-        <v>92.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -611,31 +611,31 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>89.5</v>
+        <v>68</v>
       </c>
       <c r="J4" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K4" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="K4" t="n">
-        <v>100.5</v>
-      </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -657,31 +657,31 @@
         <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="G5" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>92.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J5" t="n">
-        <v>92.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>92.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity_Output/Best_Per_Method.xlsx
+++ b/Sensitivity_Output/Best_Per_Method.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,72 +417,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
@@ -528,13 +516,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>73.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="J2" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -574,13 +562,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="J3" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K3" t="n">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -614,19 +602,19 @@
         <v>0.26</v>
       </c>
       <c r="G4" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>65.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="K4" t="n">
-        <v>87.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -666,13 +654,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="J5" t="n">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K5" t="n">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Best_Per_Method.xlsx
+++ b/Sensitivity_Output/Best_Per_Method.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>alpha</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>lookahead_days</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>total_assigned</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_avg_utilization</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_avg_utilization</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_avg_utilization</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>HomecareA_overcap_weeks</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>HomecareB_overcap_weeks</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HomecareC_overcap_weeks</t>
         </is>
